--- a/usuarios_dashboard.xlsx
+++ b/usuarios_dashboard.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G209"/>
+  <dimension ref="A1:G215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8129,7 +8129,181 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Creado</t>
+          <t>Actualizado</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>lider</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>NATHALY AGUILAR</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Nathaly Aguilar</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Nuevo: revisa NOMBRE (Nombres Apellidos) y pon CREAR = SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>lider</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>OSPINO ARAUJO ALEXANDER</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Ospino Araujo Alexander</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Nuevo: revisa NOMBRE (Nombres Apellidos) y pon CREAR = SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>ARBEY ALONSO ALVAREZ</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Arbey Alonso Alvarez</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Nuevo: revisa NOMBRE (Nombres Apellidos) y pon CREAR = SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>FRANCI VALENCIA</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Franci Valencia</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Nuevo: revisa NOMBRE (Nombres Apellidos) y pon CREAR = SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>JOHN ALEXANDER LÓPEZ BELLO</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>John Alexander López Bello</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Nuevo: revisa NOMBRE (Nombres Apellidos) y pon CREAR = SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>MARTINEZ VARGAS CHRISTAN RICARDO</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Martinez Vargas Christan Ricardo</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Nuevo: revisa NOMBRE (Nombres Apellidos) y pon CREAR = SI</t>
         </is>
       </c>
     </row>

--- a/usuarios_dashboard.xlsx
+++ b/usuarios_dashboard.xlsx
@@ -8149,16 +8149,24 @@
           <t>Nathaly Aguilar</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
-      <c r="E210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>NAGUILAR</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>NaAg523*</t>
+        </is>
+      </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>REVISAR</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Nuevo: revisa NOMBRE (Nombres Apellidos) y pon CREAR = SI</t>
+          <t>Creado</t>
         </is>
       </c>
     </row>
@@ -8178,16 +8186,24 @@
           <t>Ospino Araujo Alexander</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
-      <c r="E211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>OARAUJO</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>OsAr901*</t>
+        </is>
+      </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>REVISAR</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Nuevo: revisa NOMBRE (Nombres Apellidos) y pon CREAR = SI</t>
+          <t>Creado</t>
         </is>
       </c>
     </row>
@@ -8207,16 +8223,24 @@
           <t>Arbey Alonso Alvarez</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
-      <c r="E212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>AALONSO</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>ArAl291*</t>
+        </is>
+      </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>REVISAR</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Nuevo: revisa NOMBRE (Nombres Apellidos) y pon CREAR = SI</t>
+          <t>Creado</t>
         </is>
       </c>
     </row>
@@ -8236,16 +8260,24 @@
           <t>Franci Valencia</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>FVALENCIA</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>FrVa363*</t>
+        </is>
+      </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>REVISAR</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Nuevo: revisa NOMBRE (Nombres Apellidos) y pon CREAR = SI</t>
+          <t>Creado</t>
         </is>
       </c>
     </row>
@@ -8265,16 +8297,24 @@
           <t>John Alexander López Bello</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
-      <c r="E214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>JALOPEZ</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>JoLo914*</t>
+        </is>
+      </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>REVISAR</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Nuevo: revisa NOMBRE (Nombres Apellidos) y pon CREAR = SI</t>
+          <t>Creado</t>
         </is>
       </c>
     </row>
@@ -8294,16 +8334,24 @@
           <t>Martinez Vargas Christan Ricardo</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
-      <c r="E215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>MVCHRISTAN</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>MaCh082*</t>
+        </is>
+      </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>REVISAR</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Nuevo: revisa NOMBRE (Nombres Apellidos) y pon CREAR = SI</t>
+          <t>Creado</t>
         </is>
       </c>
     </row>
